--- a/ref/ref_unor.xlsx
+++ b/ref/ref_unor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dinaskominfo/kiken/Project/next/e-office2026/ref/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B5DAF2-D3A5-D041-AF00-582FD36C1E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A80C8C5-B37B-8C46-BBAB-C33CC5D081C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15240" xr2:uid="{7DB80866-006F-164E-9C02-100CA74B9EA0}"/>
   </bookViews>
